--- a/hardware/bom/RescueSwarm_BOM_India.xlsx
+++ b/hardware/bom/RescueSwarm_BOM_India.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="C7" s="49" t="inlineStr">
         <is>
-          <t>Roughly 90% of line items have a real Indian supplier, but only about 60% of PROGRAMME VALUE is Indian, and about 57% of flight-hardware value. The gap is not evasion — it is what happens when Indian-designed boards carry imported silicon. Four things have no Indian option at all: the AI inference SoM (no Indian GPU/NPU at this class), high-drain 21700 cells at 45 A, 802.11/LoRa RF chipsets, and high-current connectors. Tab 09 computes all of this from the line items, so the number you quote to evaluators is one you can defend.</t>
+          <t>Roughly 90% of line items have a real Indian supplier, and about 68% of PROGRAMME VALUE is Indian, against about 59% of flight-hardware value. The gap is not evasion - it is what happens when Indian-designed boards carry imported silicon. Four things have no Indian option at all: the AI inference SoM (no Indian GPU/NPU at this class), high-drain 21700 cells at 45 A, 802.11/LoRa RF chipsets, and high-current connectors. Tab 09 computes all of this from the line items, so the number you quote to evaluators is one you can defend. Do not transcribe it into a slide and leave it there - re-read tab 09 every time the BOM changes.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
     <row r="31" ht="25.5" customHeight="1" s="45">
       <c r="B31" s="85" t="inlineStr">
         <is>
-          <t>Lead with the number, not the slogan. "84% of system value is Indian, and here are the four things that are not, and why" beats "Made in India" every time.</t>
+          <t>Lead with the number, not the slogan. "68% of programme value is Indian, and here are the four things that are not, and why" beats "Made in India" every time. Read the number off row 11 of this tab rather than from memory - the figure that used to sit in this sentence was 84%, which this tab has never computed.</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="C41" s="54" t="inlineStr">
         <is>
-          <t>Edge AI module, &gt;=20 TOPS, for tiled YOLO inference</t>
+          <t>Orin Nano-class module, &gt;=20 TOPS, on an Indian carrier</t>
         </is>
       </c>
       <c r="D41" s="54" t="inlineStr">
         <is>
-          <t>e-con Systems Darsi-class India-built edge AI box, or a VVDN / Syrma SGS built carrier around an imported SoM</t>
+          <t>Imported SoM on a VVDN / Syrma SGS / e-con built carrier; Indian enclosure and thermal design</t>
         </is>
       </c>
       <c r="E41" s="60" t="inlineStr">
@@ -3615,7 +3615,7 @@
         <v/>
       </c>
       <c r="J41" s="58" t="n">
-        <v>55000</v>
+        <v>38000</v>
       </c>
       <c r="K41" s="58">
         <f>G41*J41</f>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="N41" s="54" t="inlineStr">
         <is>
-          <t>Sizing §8.2: tiled inference at 2 Hz needs ~24 inferences/s at 640x640.</t>
+          <t>Sizing S8.2: tiled inference at 2 Hz needs ~24 inferences/s at 640x640, which S8.2 sizes on an Orin Nano. Buy the module the model assumes, on an Indian carrier -- not an integrated edge-AI box priced for a class the mission does not use. QUOTE REQUIRED.</t>
         </is>
       </c>
       <c r="O41" s="54" t="inlineStr">
@@ -4580,135 +4580,135 @@
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="45">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="44" t="inlineStr">
         <is>
           <t>SAFETY</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="44" t="inlineStr">
         <is>
           <t>Recovery parachute</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="44" t="inlineStr">
         <is>
           <t>Ballistic/CO2 or spring-deployed canopy sized for 6 kg AUW, &lt;20 m deployment altitude</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>Indian UAV-parachute supplier (TBD)</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="44" t="inlineStr">
         <is>
           <t>I2</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="44" t="n">
         <v>0.6</v>
       </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="n">
+      <c r="G59" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="44" t="n">
         <v>240</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="44">
         <f>G59*H59</f>
         <v/>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" s="44" t="n">
         <v>12000</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="44">
         <f>G59*J59</f>
         <v/>
       </c>
-      <c r="L59">
+      <c r="L59" s="44">
         <f>K59*F59</f>
         <v/>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M59" s="44" t="inlineStr">
         <is>
           <t>3-4 wk</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N59" s="44" t="inlineStr">
         <is>
           <t>SYS-41. Organisers confirmed a recovery parachute is permitted, ballistic/CO2 included. A crash costs -50; landing outside the pad costs -10, so deploying is worth ~40 points even accepting the penalty. Armed above 20 m, inhibited below (it cannot inflate lower).</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O59" s="44" t="inlineStr">
         <is>
           <t>Canopy fabric and the gas cartridge are likely imported.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="44" t="n">
         <v>49</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="44" t="inlineStr">
         <is>
           <t>Parachute mount + bridle</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="44" t="inlineStr">
         <is>
           <t>Top-centre mount, Kevlar bridle to the frame centre plate, clear deployment cone</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="44" t="inlineStr">
         <is>
           <t>In-house + local machining</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="44" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" t="n">
+      <c r="F60" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="44" t="n">
         <v>60</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="44">
         <f>G60*H60</f>
         <v/>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" s="44" t="n">
         <v>1500</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="44">
         <f>G60*J60</f>
         <v/>
       </c>
-      <c r="L60">
+      <c r="L60" s="44">
         <f>K60*F60</f>
         <v/>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M60" s="44" t="inlineStr">
         <is>
           <t>1 wk</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N60" s="44" t="inlineStr">
         <is>
           <t>Must be designed into the frame, not retrofitted: a bolted-on mount fouls a prop or fires into an arm. Top-centre, clear deployment cone. See frame-design-constraints.md item 5.</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O60" s="44" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="C5" s="54" t="inlineStr">
         <is>
-          <t>16 GB RAM, discrete GPU, 1 TB SSD</t>
+          <t>16 GB RAM, 1 TB SSD, hardware H.264 decode</t>
         </is>
       </c>
       <c r="D5" s="54" t="inlineStr">
@@ -5697,7 +5697,7 @@
         <v/>
       </c>
       <c r="J5" s="58" t="n">
-        <v>105000</v>
+        <v>85000</v>
       </c>
       <c r="K5" s="58">
         <f>G5*J5</f>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="N5" s="54" t="inlineStr">
         <is>
-          <t>Runs the custom GCS, MAVLink router, mesh node and video decode. Rule C10 permits exactly ONE GCS.</t>
+          <t>Runs the custom GCS, MAVLink router, mesh node and video decode. Rule C10 permits exactly ONE GCS. The load is 3 x 720p H.264 WebRTC decode plus a Python GCS -- any modern iGPU does that. Detector training moved to Indian GPU cloud (tab 06 line 13), so no machine here needs a discrete GPU.</t>
         </is>
       </c>
       <c r="O5" s="54" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C6" s="54" t="inlineStr">
         <is>
-          <t>Cloned image, ready to swap</t>
+          <t>Cloned image, ready to swap; same software, lower spec</t>
         </is>
       </c>
       <c r="D6" s="54" t="inlineStr">
@@ -5761,7 +5761,7 @@
         <v/>
       </c>
       <c r="J6" s="58" t="n">
-        <v>85000</v>
+        <v>55000</v>
       </c>
       <c r="K6" s="58">
         <f>G6*J6</f>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="N6" s="54" t="inlineStr">
         <is>
-          <t>A GCS failure ends the mission. Clone it and keep it powered in the field box.</t>
+          <t>A GCS failure ends the mission. Clone it and keep it powered in the field box. It has to run the same software, not match the same benchmark -- a second full-price machine buys nothing the swap does not already give.</t>
         </is>
       </c>
       <c r="O6" s="54" t="inlineStr">
@@ -5825,7 +5825,7 @@
         <v/>
       </c>
       <c r="J7" s="58" t="n">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="K7" s="58">
         <f>G7*J7</f>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="N7" s="54" t="inlineStr">
         <is>
-          <t>You cannot read a laptop screen in Indian midday sun (rule C15: daylight outdoors). Judges watch this screen.</t>
+          <t>You cannot read a laptop screen in Indian midday sun (rule C15: daylight outdoors). Judges watch this screen. Hood is locally fabricated; the monitor is a commodity 15 in portable panel.</t>
         </is>
       </c>
       <c r="O7" s="54" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C18" s="54" t="inlineStr">
         <is>
-          <t>1.5-2 kWh LiFePO4 with AC output</t>
+          <t>1.2 kWh LiFePO4 with AC output</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
@@ -6400,7 +6400,7 @@
         <v/>
       </c>
       <c r="J18" s="58" t="n">
-        <v>80000</v>
+        <v>55000</v>
       </c>
       <c r="K18" s="58">
         <f>G18*J18</f>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="N18" s="54" t="inlineStr">
         <is>
-          <t>Charging 3 x ~292 Wh packs between sorties plus GCS and instruments; a test day is 6-10 sorties.</t>
+          <t>Sized on the actual energy: 3 x 292 Wh packs at ~85 % charge efficiency is ~1.03 kWh, plus GCS and instruments. 1.2 kWh covers a sortie set and recharges off mains or a vehicle between them; 2 kWh was carrying a reserve nothing asked for.</t>
         </is>
       </c>
       <c r="O18" s="54" t="inlineStr">
@@ -6454,7 +6454,7 @@
         <v>0.9</v>
       </c>
       <c r="G19" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="57" t="n">
         <v>6000</v>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="N19" s="54" t="inlineStr">
         <is>
-          <t>Optional; useful for remote P7 data-campaign sites.</t>
+          <t>CUT. The BOM's own note called this optional, and 200 W of folding PV needs ~7 h of ideal sun to refill 1.2 kWh -- that is not an operational answer for a test day. Mains, a vehicle inverter or a hired genset covers remote P7 sites. Reinstate at INR 15,000 if a site has neither.</t>
         </is>
       </c>
       <c r="O19" s="54" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>Indian case maker (e.g. Aristo / local) + local foam cutting</t>
+          <t>Local case maker + local foam cutting (Indian case maker if quoted competitively)</t>
         </is>
       </c>
       <c r="E23" s="55" t="inlineStr">
@@ -6720,7 +6720,7 @@
         <v/>
       </c>
       <c r="J23" s="58" t="n">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="K23" s="58">
         <f>G23*J23</f>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="N23" s="54" t="inlineStr">
         <is>
-          <t>Sizing §15: the 5-minute setup starts with getting aircraft out of cases. Foam layout is part of the choreography.</t>
+          <t>Sizing S15: the 5-minute setup starts with getting aircraft out of cases. Foam layout is part of the choreography -- which is a function of the foam, not the shell. Locally fabricated wheeled cases meet it. QUOTE REQUIRED.</t>
         </is>
       </c>
       <c r="O23" s="54" t="inlineStr">
@@ -7417,7 +7417,7 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="57" t="n">
         <v>180</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="N6" s="54" t="inlineStr">
         <is>
-          <t>Measures real hover current against the 36 A predicted (Sizing §6).</t>
+          <t>Measures real hover current against the 36 A predicted (Sizing S6). One instrument, used on one thrust stand, by one person.</t>
         </is>
       </c>
       <c r="O6" s="54" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="C7" s="54" t="inlineStr">
         <is>
-          <t>6S, 300-1000 W, balance charging, 2 units</t>
+          <t>6S, 400-600 W, balance charging, 2 units</t>
         </is>
       </c>
       <c r="D7" s="54" t="inlineStr">
@@ -7491,7 +7491,7 @@
         <v/>
       </c>
       <c r="J7" s="58" t="n">
-        <v>26000</v>
+        <v>14000</v>
       </c>
       <c r="K7" s="58">
         <f>G7*J7</f>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="N7" s="54" t="inlineStr">
         <is>
-          <t>A 292 Wh pack at 1C needs ~300 W. Two chargers keep a test day moving.</t>
+          <t>A 292 Wh pack at 1C needs ~300 W. Two chargers keep a test day moving. The 1000 W class was buying headroom above 1C that the cells should not see anyway -- 400-600 W each is the requirement.</t>
         </is>
       </c>
       <c r="O7" s="54" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C8" s="54" t="inlineStr">
         <is>
-          <t>24 V 40 A bench/server supply</t>
+          <t>24 V 40 A bench/server supply (960 W, feeds both chargers)</t>
         </is>
       </c>
       <c r="D8" s="54" t="inlineStr">
@@ -7545,7 +7545,7 @@
         <v>0.8</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="57" t="n">
         <v>1500</v>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="N8" s="54" t="inlineStr">
         <is>
-          <t>Feeds the chargers at rated power.</t>
+          <t>Feeds the chargers at rated power. Two 600 W chargers at 1C draw ~600 W combined, so one 960 W supply carries both with margin.</t>
         </is>
       </c>
       <c r="O8" s="54" t="inlineStr">
@@ -7673,7 +7673,7 @@
         <v>0.4</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="57" t="n">
         <v>3500</v>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="N10" s="54" t="inlineStr">
         <is>
-          <t>Soldering directly to cells damages them.</t>
+          <t>CUT. Tab 01 line 18 buys pack assembly as a service from an Indian pack house, which spot-welds. Owning a welder to do in-house what is already being paid for is a duplicate buy. Reinstate at INR 15,000 only if pack assembly is brought in-house.</t>
         </is>
       </c>
       <c r="O10" s="54" t="inlineStr">
@@ -7886,7 +7886,7 @@
         <v>0.8</v>
       </c>
       <c r="G14" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="57" t="n">
         <v>300</v>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="N14" s="54" t="inlineStr">
         <is>
-          <t>CF tube OD/ID verification.</t>
+          <t>CF tube OD/ID verification. One set; this is a bench measurement, not two parallel stations.</t>
         </is>
       </c>
       <c r="O14" s="54" t="inlineStr">
@@ -8632,7 +8632,7 @@
         <v>0.2</v>
       </c>
       <c r="G27" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="57" t="n">
         <v>0</v>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="N27" s="54" t="inlineStr">
         <is>
-          <t>Development Plan P4/P7: 200-run Monte Carlo campaigns and detector training.</t>
+          <t>CUT -- the largest single line in the programme. Detector training and the 200-run Monte Carlo move to Indian GPU cloud (tab 06 line 13, raised to INR 75,000). Cloud is cheaper than the capex, and MORE indigenous: E2E / Yotta / NxtGen score I1 at 0.9 against I3 at 0.2 for an assembled RTX box. Annotation (CVAT) and SITL run on the two GCS laptops. Reinstate at INR 165,000 only if sustained offline training becomes the bottleneck.</t>
         </is>
       </c>
       <c r="O27" s="54" t="inlineStr">
@@ -9328,7 +9328,7 @@
         <v/>
       </c>
       <c r="J11" s="58" t="n">
-        <v>55000</v>
+        <v>38000</v>
       </c>
       <c r="K11" s="58">
         <f>G11*J11</f>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="N11" s="54" t="inlineStr">
         <is>
-          <t>Sizing §15: never build the inference engine at boot. The spare must be imaged and warm-cached too.</t>
+          <t>Sizing S15: never build the inference engine at boot. The spare must be imaged and warm-cached too. Tracks tab 01 line 33.</t>
         </is>
       </c>
       <c r="O11" s="54" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="B14" s="54" t="inlineStr">
         <is>
-          <t>COMPLETE SPARE AIRCRAFT</t>
+          <t>Spare airframe structure set</t>
         </is>
       </c>
       <c r="C14" s="54" t="inlineStr">
         <is>
-          <t>Fourth airframe, built and flight-tested</t>
+          <t>Fourth frame kit: arms, clamps, centre plates, motor mounts, landing gear, tray, canopy, fasteners</t>
         </is>
       </c>
       <c r="D14" s="54" t="inlineStr">
@@ -9507,20 +9507,20 @@
         </is>
       </c>
       <c r="F14" s="56" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G14" s="53" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="57" t="n">
-        <v>5700</v>
+        <v>1300</v>
       </c>
       <c r="I14" s="57">
         <f>G14*H14</f>
         <v/>
       </c>
       <c r="J14" s="58" t="n">
-        <v>165000</v>
+        <v>25000</v>
       </c>
       <c r="K14" s="58">
         <f>G14*J14</f>
@@ -9532,17 +9532,17 @@
       </c>
       <c r="M14" s="53" t="inlineStr">
         <is>
-          <t>8 wk</t>
+          <t>3 wk</t>
         </is>
       </c>
       <c r="N14" s="54" t="inlineStr">
         <is>
-          <t>STRONGLY RECOMMENDED. Rule C1 needs only 2 flying, but a pre-flight failure on finals day with no spare means flying 2 and losing coverage.</t>
+          <t>REPLACES the INR 1.65 L complete fourth aircraft. Lines 1-9 above already hold a full set of motors, ESCs, props, arms, FC, GNSS, compute, camera and three packs -- INR 2.1 L, i.e. everything a fourth airframe needs EXCEPT the structure. Buying a whole aircraft on top of that bought most of it twice. This line buys the missing half, and its 2-3 wk lead is the part that cannot be compressed after a crash.</t>
         </is>
       </c>
       <c r="O14" s="54" t="inlineStr">
         <is>
-          <t>Domestic supply makes this far more affordable than with imported parts.</t>
+          <t>RISK ACCEPTED: rebuilding consumes the spares, so a second failure in the same week is uncovered. Rule C1 needs only 2 aircraft flying. Reinstate the complete fourth aircraft at INR 165,000 if funding allows -- it is a schedule hedge, not a capability.</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="C18" s="54" t="inlineStr">
         <is>
-          <t>GPU hours for detector training</t>
+          <t>GPU hours for detector training and the SITL Monte Carlo</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
@@ -10952,7 +10952,7 @@
         <v/>
       </c>
       <c r="J18" s="58" t="n">
-        <v>40000</v>
+        <v>75000</v>
       </c>
       <c r="K18" s="58">
         <f>G18*J18</f>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="N18" s="54" t="inlineStr">
         <is>
-          <t>A genuinely indigenous option for training compute, unlike inference silicon.</t>
+          <t>A genuinely indigenous option for training compute, unlike inference silicon. Raised from INR 40,000 to absorb the cut dev workstation (tab 04 line 20): net saving INR 1.30 L, and it moves INR 75,000 of spend from I3 0.2 to I1 0.9.</t>
         </is>
       </c>
       <c r="O18" s="54" t="inlineStr">
@@ -11561,25 +11561,25 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>Safety (recovery parachute)</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="44" t="n">
         <v>300</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="44">
         <f>D13-C13</f>
         <v/>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="44" t="inlineStr">
         <is>
           <t>SYS-41. Not in the sizing model when written; the model has since been updated to match.</t>
         </is>
@@ -11735,7 +11735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="44" min="1" max="1"/>
@@ -12070,7 +12070,7 @@
     <row r="20" ht="15" customHeight="1" s="45">
       <c r="B20" s="71" t="inlineStr">
         <is>
-          <t>Indian sourcing cuts the dutiable import base sharply — duty and freight fall from ~INR 5.9 L to a fraction of that.</t>
+          <t>Indian sourcing cuts the dutiable import base sharply: duty and freight are ~INR 1.34 L on the imported residual, against ~INR 4.17 L if the same BOM were bought fully imported.</t>
         </is>
       </c>
     </row>
@@ -12099,6 +12099,13 @@
       <c r="B24" s="71" t="inlineStr">
         <is>
           <t>Send RFQs to Bharath Components, Mechtex, Flameback Tech, S R Aerospace, Agam Robotics, Zuppa, Teravolt Labs, Accord Software, e-con Systems, FxUAV and an Indian pack house in Phase 0 week 1. Several do not publish prices, and lead-time discovery matters more than price discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>COST PASS 2026-08-10: subtotal cut from INR 24.06 L to INR 18.96 L (-21%), programme total INR 36.97 L to INR 28.74 L (-22%), indigenisation 61.3% to 67.9%. Nothing was cut from the flight-critical path and no flight mass changed. The cuts were duplicate buys (dev workstation vs Indian GPU cloud; a complete fourth aircraft on top of a full spares set; a spot welder against outsourced pack assembly), items the BOM itself called optional (solar panel), quantities of bench instruments bought in twos, and lines specified above their own stated requirement (AI compute, GCS laptops, power station, chargers). Cut lines are held at Qty 0 with their price intact - reinstating one is a single-cell edit. See hardware/bom/CHANGELOG.md.</t>
         </is>
       </c>
     </row>

--- a/hardware/bom/RescueSwarm_BOM_India.xlsx
+++ b/hardware/bom/RescueSwarm_BOM_India.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -95,6 +95,17 @@
       <family val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -175,7 +186,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -431,6 +442,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1307,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="44" min="1" max="1"/>
@@ -1324,6 +1347,8 @@
     <col width="9" customWidth="1" style="44" min="13" max="13"/>
     <col width="54" customWidth="1" style="44" min="14" max="14"/>
     <col width="44" customWidth="1" style="44" min="15" max="15"/>
+    <col width="46" customWidth="1" style="45" min="16" max="16"/>
+    <col width="60" customWidth="1" style="45" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="45">
@@ -1421,6 +1446,17 @@
       <c r="O3" s="50" t="inlineStr">
         <is>
           <t>Indigenisation gap or action</t>
+        </is>
+      </c>
+      <c r="P3" s="86" t="inlineStr">
+        <is>
+          <t>Source link</t>
+        </is>
+      </c>
+      <c r="Q3" s="86" t="inlineStr">
+        <is>
+          <t>Sourcing note
+(verified 2026-08-10)</t>
         </is>
       </c>
     </row>
@@ -1508,6 +1544,16 @@
           <t>Carbon precursor fibre is imported (Epsilon Carbon is commissioning Indian PAN fibre). Weave and pultrusion are Indian.</t>
         </is>
       </c>
+      <c r="P5" s="87" t="inlineStr">
+        <is>
+          <t>https://www.kinecokamanindia.com/</t>
+        </is>
+      </c>
+      <c r="Q5" s="88" t="inlineStr">
+        <is>
+          <t>Fabricator, not a catalogue part. Quote to drawing. Aerospace CF, Pilerne Goa.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="23.85" customHeight="1" s="45">
       <c r="A6" s="53" t="n">
@@ -1572,6 +1618,16 @@
           <t>Same fibre-origin caveat as the tubes.</t>
         </is>
       </c>
+      <c r="P6" s="87" t="inlineStr">
+        <is>
+          <t>https://www.compositestechnologypark.com/about.html</t>
+        </is>
+      </c>
+      <c r="Q6" s="88" t="inlineStr">
+        <is>
+          <t>Fabricator. CNC-cut CF sandwich to drawing.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="35.05" customHeight="1" s="45">
       <c r="A7" s="53" t="n">
@@ -1636,6 +1692,12 @@
           <t>None. India has deep small-batch CNC capacity.</t>
         </is>
       </c>
+      <c r="P7" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q7" s="88" t="n"/>
     </row>
     <row r="8" ht="23.85" customHeight="1" s="45">
       <c r="A8" s="53" t="n">
@@ -1700,6 +1762,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P8" s="87" t="inlineStr">
+        <is>
+          <t>https://www.compositestechnologypark.com/about.html</t>
+        </is>
+      </c>
+      <c r="Q8" s="88" t="inlineStr">
+        <is>
+          <t>Fabricator. Same source as the centre plate.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.85" customHeight="1" s="45">
       <c r="A9" s="53" t="n">
@@ -1764,6 +1836,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P9" s="87" t="inlineStr">
+        <is>
+          <t>https://www.kinecokamanindia.com/</t>
+        </is>
+      </c>
+      <c r="Q9" s="88" t="inlineStr">
+        <is>
+          <t>Fabricator. Same source as the arm tube.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.85" customHeight="1" s="45">
       <c r="A10" s="53" t="n">
@@ -1828,6 +1910,12 @@
           <t>Filament: WOL3D / Fila3D (Indian extruders, imported resin pellets).</t>
         </is>
       </c>
+      <c r="P10" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q10" s="88" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="45">
       <c r="A11" s="53" t="n">
@@ -1892,6 +1980,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P11" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q11" s="88" t="n"/>
     </row>
     <row r="12" ht="23.85" customHeight="1" s="45">
       <c r="A12" s="53" t="n">
@@ -1956,6 +2050,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P12" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q12" s="88" t="n"/>
     </row>
     <row r="13" ht="23.85" customHeight="1" s="45">
       <c r="A13" s="53" t="n">
@@ -2020,6 +2120,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P13" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q13" s="88" t="n"/>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="45">
       <c r="A14" s="53" t="n">
@@ -2084,6 +2190,12 @@
           <t>Small DC fans are largely imported; duct and integration are Indian.</t>
         </is>
       </c>
+      <c r="P14" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q14" s="88" t="n"/>
     </row>
     <row r="15" ht="23.85" customHeight="1" s="45">
       <c r="A15" s="53" t="n">
@@ -2148,6 +2260,16 @@
           <t>None. Indian fastener manufacture is world class.</t>
         </is>
       </c>
+      <c r="P15" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q15" s="88" t="inlineStr">
+        <is>
+          <t>Sundram Fasteners named in col D but not verified against a catalogue page.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.85" customHeight="1" s="45">
       <c r="A16" s="53" t="n">
@@ -2212,6 +2334,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P16" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q16" s="88" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="45">
       <c r="A17" s="51" t="inlineStr">
@@ -2297,6 +2425,16 @@
           <t>Magnets and some bearings imported. Winding, stator, housing and assembly are Indian. Request a measured thrust/current curve with the quote.</t>
         </is>
       </c>
+      <c r="P18" s="87" t="inlineStr">
+        <is>
+          <t>https://bharathcomponents.com/buy-bldc-motor/</t>
+        </is>
+      </c>
+      <c r="Q18" s="88" t="inlineStr">
+        <is>
+          <t>150 KV variant confirmed in catalogue, inside the 150-190 KV spec. Spec sheet: iotechworld.co.in/150kv-bharath-drone-bldc-motor.htm. Subsidiary of IoTechWorld. PRICE NOT PUBLISHED - quote required.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.85" customHeight="1" s="45">
       <c r="A19" s="53" t="n">
@@ -2361,6 +2499,16 @@
           <t>MOSFETs and the MCU are imported silicon; board design, firmware and manufacture are Indian.</t>
         </is>
       </c>
+      <c r="P19" s="87" t="inlineStr">
+        <is>
+          <t>https://www.flamebacktech.com/esc</t>
+        </is>
+      </c>
+      <c r="Q19" s="88" t="inlineStr">
+        <is>
+          <t>CAUTION: catalogue advertises 30-45 A. This line specifies 60 A. Confirm a 60 A part exists before ordering.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="35.05" customHeight="1" s="45">
       <c r="A20" s="53" t="n">
@@ -2425,6 +2573,16 @@
           <t>CSIR-NAL certification is a genuine quality signal. Fibre imported; layup and moulding Indian.</t>
         </is>
       </c>
+      <c r="P20" s="87" t="inlineStr">
+        <is>
+          <t>https://www.sraeros.com/drone-propeller.html</t>
+        </is>
+      </c>
+      <c r="Q20" s="88" t="inlineStr">
+        <is>
+          <t>CSIR-NAL certification claim confirmed on site. 18 in folding variant NOT confirmed in catalogue - confirm size and folding hub.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.85" customHeight="1" s="45">
       <c r="A21" s="53" t="n">
@@ -2487,6 +2645,16 @@
       <c r="O21" s="54" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P21" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q21" s="88" t="inlineStr">
+        <is>
+          <t>Supplied with motor per col D - confirm inclusion at order.</t>
         </is>
       </c>
     </row>
@@ -2574,6 +2742,16 @@
           <t>WEAKEST INDIGENISATION LINK. GODI makes BIS-certified 21700 NMC in India, but confirm a 40 A+ continuous drone-grade variant exists. If not, use an Indian-assembled pack with imported high-drain cells (tier I3) and say so openly — that is still the honest Indian best.</t>
         </is>
       </c>
+      <c r="P23" s="87" t="inlineStr">
+        <is>
+          <t>https://evreporter.com/godi-receives-bis-certification-to-sell-li-ion-cells-in-india/</t>
+        </is>
+      </c>
+      <c r="Q23" s="88" t="inlineStr">
+        <is>
+          <t>BIS certification for 21700 NMC811 confirmed. NO public product page and NO published price - direct quote required. Weakest indigenisation link per col O.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="35.05" customHeight="1" s="45">
       <c r="A24" s="53" t="n">
@@ -2638,6 +2816,16 @@
           <t>Have them capacity- and IR-match every cell and give you the data.</t>
         </is>
       </c>
+      <c r="P24" s="87" t="inlineStr">
+        <is>
+          <t>https://revogreenbatteries.com/pages/custom-batteries</t>
+        </is>
+      </c>
+      <c r="Q24" s="88" t="inlineStr">
+        <is>
+          <t>Custom pack service confirmed (Pune). Alternate: lionbattery.in/lithium-battery-for-drones/</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.85" customHeight="1" s="45">
       <c r="A25" s="53" t="n">
@@ -2702,6 +2890,16 @@
           <t>Protection ICs imported.</t>
         </is>
       </c>
+      <c r="P25" s="87" t="inlineStr">
+        <is>
+          <t>https://www.flamebacktech.com/</t>
+        </is>
+      </c>
+      <c r="Q25" s="88" t="inlineStr">
+        <is>
+          <t>BMS listed in product range; no dedicated 6S product page found.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.85" customHeight="1" s="45">
       <c r="A26" s="53" t="n">
@@ -2766,6 +2964,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P26" s="87" t="inlineStr">
+        <is>
+          <t>https://www.flamebacktech.com/</t>
+        </is>
+      </c>
+      <c r="Q26" s="88" t="inlineStr">
+        <is>
+          <t>PDB listed in product range; 200 A rating not confirmed on a product page.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.85" customHeight="1" s="45">
       <c r="A27" s="53" t="n">
@@ -2830,6 +3038,16 @@
           <t>Hall sensor IC imported.</t>
         </is>
       </c>
+      <c r="P27" s="87" t="inlineStr">
+        <is>
+          <t>https://www.flamebacktech.com/</t>
+        </is>
+      </c>
+      <c r="Q27" s="88" t="inlineStr">
+        <is>
+          <t>Alternate: bharathcomponents.com. Rating not confirmed on a product page.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.85" customHeight="1" s="45">
       <c r="A28" s="53" t="n">
@@ -2894,6 +3112,16 @@
           <t>Regulator ICs imported.</t>
         </is>
       </c>
+      <c r="P28" s="87" t="inlineStr">
+        <is>
+          <t>https://www.flamebacktech.com/</t>
+        </is>
+      </c>
+      <c r="Q28" s="88" t="inlineStr">
+        <is>
+          <t>Rating not confirmed on a product page.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.85" customHeight="1" s="45">
       <c r="A29" s="53" t="n">
@@ -2958,6 +3186,16 @@
           <t>None. Indian cable manufacture is excellent.</t>
         </is>
       </c>
+      <c r="P29" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q29" s="88" t="inlineStr">
+        <is>
+          <t>Polycab / Finolex / RR Kabel named in col D; commodity, price at order.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="35.05" customHeight="1" s="45">
       <c r="A30" s="53" t="n">
@@ -3022,6 +3260,16 @@
           <t>NO INDIAN EQUIVALENT for XT90-S / JST-GH class connectors. Small value, unavoidable import. Buy through an Indian distributor.</t>
         </is>
       </c>
+      <c r="P30" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q30" s="88" t="inlineStr">
+        <is>
+          <t>XT90-S class. Col O already records NO INDIAN EQUIVALENT.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="45">
       <c r="A31" s="53" t="n">
@@ -3086,6 +3334,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P31" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q31" s="88" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="45">
       <c r="A32" s="51" t="inlineStr">
@@ -3171,6 +3425,16 @@
           <t>NXP i.MXRT MCU imported; board design, firmware, secure element integration and manufacture are Indian. ALTERNATIVE: Zuppa NavGati (Chennai), which runs on C-DAC-developed PCBs and processors — higher indigenisation, less open-ecosystem tooling.</t>
         </is>
       </c>
+      <c r="P33" s="87" t="inlineStr">
+        <is>
+          <t>https://www.agamrobotics.com/agamautopilotv6x-rt</t>
+        </is>
+      </c>
+      <c r="Q33" s="88" t="inlineStr">
+        <is>
+          <t>CONFIRMED. FMUv6X-RT, NXP i.MXRT1176 dual-core - matches col N and col O exactly. Made in India, Bengaluru. Worldwide variant: agamrobotics.com/product-page/agam-autopilot-v6x-rt-worldwide</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="35.05" customHeight="1" s="45">
       <c r="A34" s="53" t="n">
@@ -3235,6 +3499,16 @@
           <t>Fully indigenous. Scope it as a non-flight-critical subsystem with a hardware bypass.</t>
         </is>
       </c>
+      <c r="P34" s="87" t="inlineStr">
+        <is>
+          <t>https://vegaprocessors.in/</t>
+        </is>
+      </c>
+      <c r="Q34" s="88" t="inlineStr">
+        <is>
+          <t>C-DAC / MeitY DIR-V programme confirmed. SoC docs: cdac-vega.gitlab.io/socoverview/microprocessors.html. Free-kit route via NIDAR is an ASSUMPTION - confirm with organisers.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="57.45" customHeight="1" s="45">
       <c r="A35" s="53" t="n">
@@ -3299,6 +3573,16 @@
           <t>ACTION: confirm RTK and moving-baseline heading support before Phase 1 closes. If Teravolt does not support it, evaluate Accord Software &amp; Systems (Bengaluru) or Elena Geo Systems. Sizing §11 shows RTK is worth ~1.4 m of geotag accuracy.</t>
         </is>
       </c>
+      <c r="P35" s="87" t="inlineStr">
+        <is>
+          <t>https://www.teravolt.in/product-page/aeronav-1-dual-band-gnss</t>
+        </is>
+      </c>
+      <c r="Q35" s="88" t="inlineStr">
+        <is>
+          <t>PARTIAL. NavIC L1+L5 and BMM350 magnetometer confirmed. RTK AND MOVING-BASELINE ARE NOT CLAIMED ON THE PRODUCT PAGE - this is the open action in col O and it gates geotag case C. ArduPilot driver: ardupilot.org/copter/docs/common-AeroNav-1.html. Company is Chandigarh, not as implied by col D.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="35.05" customHeight="1" s="45">
       <c r="A36" s="53" t="n">
@@ -3363,6 +3647,16 @@
           <t>Same RTK confirmation action as above.</t>
         </is>
       </c>
+      <c r="P36" s="87" t="inlineStr">
+        <is>
+          <t>https://www.teravolt.in/product-page/aeronav-1-dual-band-gnss</t>
+        </is>
+      </c>
+      <c r="Q36" s="88" t="inlineStr">
+        <is>
+          <t>Same part and the same unconfirmed RTK/moving-baseline caveat as the primary.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23.85" customHeight="1" s="45">
       <c r="A37" s="53" t="n">
@@ -3427,6 +3721,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P37" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q37" s="88" t="inlineStr">
+        <is>
+          <t>Supplied with the receiver per col D - confirm inclusion.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.85" customHeight="1" s="45">
       <c r="A38" s="53" t="n">
@@ -3491,6 +3795,16 @@
           <t>ELRS silicon imported; Zerodrag manufactures in India.</t>
         </is>
       </c>
+      <c r="P38" s="87" t="inlineStr">
+        <is>
+          <t>https://zerodrag.in/products/express-lrs-receiver</t>
+        </is>
+      </c>
+      <c r="Q38" s="88" t="inlineStr">
+        <is>
+          <t>CONFIRMED. Nexus1 ELRS 2.4 GHz, diversity, made in India, 12-month warranty.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23.85" customHeight="1" s="45">
       <c r="A39" s="53" t="n">
@@ -3555,6 +3869,12 @@
           <t>NAND flash has no Indian source.</t>
         </is>
       </c>
+      <c r="P39" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q39" s="88" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="45">
       <c r="A40" s="51" t="inlineStr">
@@ -3640,6 +3960,16 @@
           <t>NO INDIAN GPU/NPU EXISTS AT THIS CLASS. This is the one genuinely irreducible import. Mitigation: Indian-designed carrier board, Indian enclosure and thermal design, Indian camera, and a model trained on Indian field data. Declare it plainly in the technical report rather than hiding it — evaluators respect an honest gap analysis more than a vague claim.</t>
         </is>
       </c>
+      <c r="P41" s="87" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/autonomous-machines/embedded-systems/jetson-orin/nano-super-developer-kit/</t>
+        </is>
+      </c>
+      <c r="Q41" s="88" t="inlineStr">
+        <is>
+          <t>Orin Nano Super, 67 TOPS - clears the &gt;=20 TOPS spec. Indian resellers: fabtolab.com, roboticsdna.in, tannatechbiz.com. NOTE: the linked SKU is the DEV KIT; this line buys a module on an Indian carrier, which is a different part and a different price. VVDN/Syrma SGS carrier per col D NOT confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="45">
       <c r="A42" s="53" t="n">
@@ -3704,6 +4034,12 @@
           <t>No Indian NAND or controller.</t>
         </is>
       </c>
+      <c r="P42" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q42" s="88" t="n"/>
     </row>
     <row r="43" ht="57.45" customHeight="1" s="45">
       <c r="A43" s="53" t="n">
@@ -3768,6 +4104,16 @@
           <t>World-class Indian embedded-vision house — 20+ years, 2 M+ cameras shipped. Sensor die (Sony/onsemi) imported; module design, ISP tuning, lens calibration and manufacture are Indian. Ask them to ISP-tune for high-altitude nadir daylight.</t>
         </is>
       </c>
+      <c r="P43" s="87" t="inlineStr">
+        <is>
+          <t>https://www.e-consystems.com/nvidia-cameras/jetson-orin-nx-cameras/12mp-sony-starvis-imx412-ultra-low-light-camera.asp</t>
+        </is>
+      </c>
+      <c r="Q43" s="88" t="inlineStr">
+        <is>
+          <t>e-CAM121_CUONX, 12 MP IMX412, MIPI CSI-2, Orin Nano compatible. S-MOUNT NOT CONFIRMED on this module - if optics are fixed, line 36 (lens) is void. Confirm before ordering both.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="23.85" customHeight="1" s="45">
       <c r="A44" s="53" t="n">
@@ -3832,6 +4178,16 @@
           <t>Optical glass largely imported.</t>
         </is>
       </c>
+      <c r="P44" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q44" s="88" t="inlineStr">
+        <is>
+          <t>See line 35 note - buying this lens assumes the camera is S-mount, which is unconfirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="23.85" customHeight="1" s="45">
       <c r="A45" s="53" t="n">
@@ -3896,6 +4252,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P45" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q45" s="88" t="n"/>
     </row>
     <row r="46" ht="23.85" customHeight="1" s="45">
       <c r="A46" s="53" t="n">
@@ -3960,6 +4322,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P46" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q46" s="88" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="45">
       <c r="A47" s="51" t="inlineStr">
@@ -4045,6 +4413,16 @@
           <t>Wi-Fi chipsets have no Indian source. FxUAV builds indigenous RF datalinks specifically to reduce this dependency — engage them early and ask what they can supply against this spec.</t>
         </is>
       </c>
+      <c r="P48" s="87" t="inlineStr">
+        <is>
+          <t>https://www.fxuav.com/</t>
+        </is>
+      </c>
+      <c r="Q48" s="88" t="inlineStr">
+        <is>
+          <t>DOES NOT MATCH. FxUAV's mesh module is advertised at 928 MHz and FxLink is 2.4 GHz point-to-point telemetry. This line specifies an 802.11s mesh at 2.4/5.8 GHz. No FxUAV product found that satisfies it. RESELECT OR REQUOTE.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="23.85" customHeight="1" s="45">
       <c r="A49" s="53" t="n">
@@ -4109,6 +4487,12 @@
           <t>Antenna manufacture is well within Indian capability.</t>
         </is>
       </c>
+      <c r="P49" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q49" s="88" t="n"/>
     </row>
     <row r="50" ht="35.05" customHeight="1" s="45">
       <c r="A50" s="53" t="n">
@@ -4173,6 +4557,16 @@
           <t>SX126x-class transceiver imported; module, firmware and integration Indian. Confirm ETA for the 865-867 MHz band.</t>
         </is>
       </c>
+      <c r="P50" s="87" t="inlineStr">
+        <is>
+          <t>https://www.fxuav.com/</t>
+        </is>
+      </c>
+      <c r="Q50" s="88" t="inlineStr">
+        <is>
+          <t>DOES NOT MATCH. FxUAV's sub-GHz mesh is 928 MHz; this line specifies 865-867 MHz, the Indian delicensed SRD band. 928 MHz is outside it. No FxUAV product found that satisfies this line. RESELECT OR REQUOTE.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="45">
       <c r="A51" s="53" t="n">
@@ -4237,6 +4631,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P51" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q51" s="88" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="45">
       <c r="A52" s="51" t="inlineStr">
@@ -4322,6 +4722,12 @@
           <t>Servo motors and ICs imported; some Indian assembly available.</t>
         </is>
       </c>
+      <c r="P53" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q53" s="88" t="n"/>
     </row>
     <row r="54" ht="23.85" customHeight="1" s="45">
       <c r="A54" s="53" t="n">
@@ -4386,6 +4792,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P54" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q54" s="88" t="n"/>
     </row>
     <row r="55" ht="23.85" customHeight="1" s="45">
       <c r="A55" s="53" t="n">
@@ -4450,6 +4862,12 @@
           <t>None.</t>
         </is>
       </c>
+      <c r="P55" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q55" s="88" t="n"/>
     </row>
     <row r="56" ht="23.85" customHeight="1" s="45">
       <c r="A56" s="53" t="n">
@@ -4514,6 +4932,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P56" s="89" t="inlineStr">
+        <is>
+          <t>Local supply - quote at order, no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q56" s="88" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1" s="45">
       <c r="A57" s="53" t="n">
@@ -4578,6 +5002,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="P57" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q57" s="88" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="45">
       <c r="A58" s="44" t="inlineStr">
@@ -4649,6 +5079,16 @@
           <t>Canopy fabric and the gas cartridge are likely imported.</t>
         </is>
       </c>
+      <c r="P59" s="87" t="inlineStr">
+        <is>
+          <t>https://fruitychutes.com/uav_rpv_drone_recovery_parachutes</t>
+        </is>
+      </c>
+      <c r="Q59" s="88" t="inlineStr">
+        <is>
+          <t>NO INDIAN SUPPLIER FOUND - col D already says TBD and it stays TBD. Nearest match is IMPORTED: Fruity Chutes Harrier, spring-launched (compatible with the no-blast ruling), RATED TO 6.2 kg AGAINST A 6.36 kg MTOW - one size undersized. Indig. 0.6 in col F is unsupported if this is imported.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="44" t="n">
@@ -4713,6 +5153,12 @@
           <t>None.</t>
         </is>
       </c>
+      <c r="P60" s="89" t="inlineStr">
+        <is>
+          <t>In-house / fabricated to drawing - no catalogue part</t>
+        </is>
+      </c>
+      <c r="Q60" s="88" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="61" t="inlineStr">
@@ -4738,6 +5184,31 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId23"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -12103,7 +12574,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>COST PASS 2026-08-10: subtotal cut from INR 24.06 L to INR 18.96 L (-21%), programme total INR 36.97 L to INR 28.74 L (-22%), indigenisation 61.3% to 67.9%. Nothing was cut from the flight-critical path and no flight mass changed. The cuts were duplicate buys (dev workstation vs Indian GPU cloud; a complete fourth aircraft on top of a full spares set; a spot welder against outsourced pack assembly), items the BOM itself called optional (solar panel), quantities of bench instruments bought in twos, and lines specified above their own stated requirement (AI compute, GCS laptops, power station, chargers). Cut lines are held at Qty 0 with their price intact - reinstating one is a single-cell edit. See hardware/bom/CHANGELOG.md.</t>
         </is>
